--- a/Tempo_results.xlsx
+++ b/Tempo_results.xlsx
@@ -2093,7 +2093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2105,6 +2105,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2153,6 +2154,11 @@
           <t>GPT-4o-mini</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>GPT-5.6-Luna-medium</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
@@ -2167,37 +2173,42 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
+          <t>gpt-5.6-luna (effort=low)</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>grok-3-mini</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen3.5-9B</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>google/gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>deepseek-reasoner</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini-2024-07-18</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
           <t>gpt-5.6-luna (effort=medium)</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>grok-3-mini</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>Qwen/Qwen3.5-9B</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="inlineStr">
-        <is>
-          <t>google/gemma-4-31B-it</t>
-        </is>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
-        <is>
-          <t>deepseek-reasoner</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="inlineStr">
-        <is>
-          <t>gemini-2.5-flash</t>
-        </is>
-      </c>
-      <c r="I2" s="8" t="inlineStr">
-        <is>
-          <t>gpt-4o-mini-2024-07-18</t>
         </is>
       </c>
     </row>
@@ -2215,6 +2226,7 @@
       <c r="G3" s="5" t="n"/>
       <c r="H3" s="5" t="n"/>
       <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2226,7 +2238,7 @@
         <v>0.7347</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.8163</v>
+        <v>0.7551</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0.8571</v>
@@ -2246,6 +2258,9 @@
       <c r="I4" s="2" t="n">
         <v>0.6122</v>
       </c>
+      <c r="J4" s="2" t="n">
+        <v>0.8163</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2257,7 +2272,7 @@
         <v>0.6429</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.75</v>
+        <v>0.8214</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0.75</v>
@@ -2277,6 +2292,9 @@
       <c r="I5" s="2" t="n">
         <v>0.4643</v>
       </c>
+      <c r="J5" s="2" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2288,7 +2306,7 @@
         <v>0.7143</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.6786</v>
+        <v>0.6964</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0.7321</v>
@@ -2308,6 +2326,9 @@
       <c r="I6" s="2" t="n">
         <v>0.4107</v>
       </c>
+      <c r="J6" s="2" t="n">
+        <v>0.6786</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2319,7 +2340,7 @@
         <v>0.5373</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.5373</v>
+        <v>0.5821</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0.6418</v>
@@ -2339,6 +2360,9 @@
       <c r="I7" s="2" t="n">
         <v>0.3582</v>
       </c>
+      <c r="J7" s="2" t="n">
+        <v>0.5373</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -2350,7 +2374,7 @@
         <v>0.65</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.675</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>0.735</v>
@@ -2369,6 +2393,9 @@
       </c>
       <c r="I8" s="4" t="n">
         <v>0.45</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>0.675</v>
       </c>
     </row>
     <row r="9">
@@ -2385,6 +2412,7 @@
       <c r="G9" s="5" t="n"/>
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2396,7 +2424,7 @@
         <v>0.78</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.7</v>
+        <v>0.62</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0.72</v>
@@ -2416,6 +2444,9 @@
       <c r="I10" s="2" t="n">
         <v>0.72</v>
       </c>
+      <c r="J10" s="2" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2427,7 +2458,7 @@
         <v>0.74</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>0.7</v>
@@ -2447,6 +2478,9 @@
       <c r="I11" s="2" t="n">
         <v>0.74</v>
       </c>
+      <c r="J11" s="2" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2458,7 +2492,7 @@
         <v>0.76</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.72</v>
+        <v>0.66</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>0.78</v>
@@ -2478,6 +2512,9 @@
       <c r="I12" s="2" t="n">
         <v>0.68</v>
       </c>
+      <c r="J12" s="2" t="n">
+        <v>0.72</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2489,7 +2526,7 @@
         <v>0.7</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.76</v>
+        <v>0.7</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>0.74</v>
@@ -2509,6 +2546,9 @@
       <c r="I13" s="2" t="n">
         <v>0.66</v>
       </c>
+      <c r="J13" s="2" t="n">
+        <v>0.76</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -2520,7 +2560,7 @@
         <v>0.745</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.745</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>0.735</v>
@@ -2540,6 +2580,9 @@
       <c r="I14" s="4" t="n">
         <v>0.7</v>
       </c>
+      <c r="J14" s="4" t="n">
+        <v>0.745</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2551,7 +2594,7 @@
         <v>0.6975</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.71</v>
+        <v>0.6875</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>0.735</v>
@@ -2570,6 +2613,9 @@
       </c>
       <c r="I15" s="4" t="n">
         <v>0.575</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>0.71</v>
       </c>
     </row>
   </sheetData>
@@ -3009,7 +3055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3025,6 +3071,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -3544,12 +3591,12 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>EMO_GPT_5.6_Luna/results_default/{EU,EA}</t>
+          <t>EMO_GPT_5.6_Luna/results/{EU,EA}</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>gpt-5.6-luna at the default medium effort. The settled effort is low, and results_eLow has EU (0.650) but no EA, so no complete EmoBench score exists at the settled config. One EA run at effort=low closes it.</t>
+          <t>gpt-5.6-luna at the settled config (reasoning_effort=low, max_completion_tokens=2048, seed 42), Quest job 9616726, 2026-10-12; 400 rows, 0 empty, 0 unparseable.</t>
         </is>
       </c>
     </row>
@@ -3561,39 +3608,39 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>XAI · Qwen · Gemma · Deepseek</t>
+          <t>GPT-5.6-Luna-medium</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>EmoBench/emobench_results.csv</t>
+          <t>EMO_GPT_5.6_Luna/results_default/{EU,EA}</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Unchanged.</t>
+          <t>gpt-5.6-luna at its default reasoning_effort=medium (max_completion_tokens=4096, seed 42), 2026-08-26. Was the OpenAI column until 2026-10-12; kept as a record, not the reported config.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>NegotiationToM</t>
+          <t>Emo</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>every column</t>
+          <t>XAI · Qwen · Gemma · Deepseek</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Interpersonal_processes_benchmarks/NegotiationToM/NEG_*/results/&lt;task&gt;/&lt;slug&gt;_shard{0..4}of5.jsonl</t>
+          <t>EmoBench/emobench_results.csv</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Added 2026-10-05, recomputed from the per-shard rows and checked equal to every NEG_*/results/&lt;slug&gt;_negotiation_overall.csv. Every column that has a number is the full 14,138 rows (desire 4,760, belief 4,760, intention 4,618) with 0 empty responses and 0 duplicate uids. Desire_EM and Belief_EM exclude the 156 rows per task whose gold is the unannotated sentinel "None" (4,604 scored); intention F1 is over all 4,618. All_EM counts a dialogue only when desire, belief and intention are all right, over 2,380 dialogues, so it is in the low hundredths by construction. Consistency_Desire / Consistency_Belief from the upstream template are out of scope (DATA_NOTES.md).</t>
+          <t>Unchanged.</t>
         </is>
       </c>
     </row>
@@ -3605,17 +3652,17 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Gemini · OpenAI</t>
+          <t>every column</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>blank — the selected pair has not run</t>
+          <t>Interpersonal_processes_benchmarks/NegotiationToM/NEG_*/results/&lt;task&gt;/&lt;slug&gt;_shard{0..4}of5.jsonl</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>NEG_Gemini_Flash3.5lite_OpenRouter and NEG_GPT_5.6_Luna exist as runners (written 2026-09-11) and have been neither piloted nor run. The NEG_Gemini and NEG_GPT runs on disk are gemini-2.5-flash and gpt-4o-mini, both superseded; their numbers are in Tempo_results.xlsx only.</t>
+          <t>Added 2026-10-05, recomputed from the per-shard rows and checked equal to every NEG_*/results/&lt;slug&gt;_negotiation_overall.csv. Every column that has a number is the full 14,138 rows (desire 4,760, belief 4,760, intention 4,618) with 0 empty responses and 0 duplicate uids. Desire_EM and Belief_EM exclude the 156 rows per task whose gold is the unannotated sentinel "None" (4,604 scored); intention F1 is over all 4,618. All_EM counts a dialogue only when desire, belief and intention are all right, over 2,380 dialogues, so it is in the low hundredths by construction. Consistency_Desire / Consistency_Belief from the upstream template are out of scope (DATA_NOTES.md).</t>
         </is>
       </c>
     </row>
@@ -3627,17 +3674,17 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>XAI = grok-3-mini</t>
+          <t>Gemini · OpenAI</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>14,138 rows — complete</t>
+          <t>blank — the selected pair has not run</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>NEG_XAI, xai_sdk, max_tokens=8192, temperature 0, 0 empty. The first full run left 12,040 rows empty when the xAI credits ran out (ISSUES.md, 2026-07-29); the current shards have none. The *.STALE_pre20260729 roll-ups and *.jsonl.bak files beside them are that earlier run and are not the source. Not in Final_result.xlsx since 2026-10-05.</t>
+          <t>NEG_Gemini_Flash3.5lite_OpenRouter and NEG_GPT_5.6_Luna exist as runners (written 2026-09-11) and have been neither piloted nor run. The NEG_Gemini and NEG_GPT runs on disk are gemini-2.5-flash and gpt-4o-mini, both superseded; their numbers are in Tempo_results.xlsx only.</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3696,7 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Qwen</t>
+          <t>XAI = grok-3-mini</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -3659,7 +3706,7 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>NEG_Qwen, 14,138 rows, 0 empty. Together, reasoning={"enabled": False}, max_tokens=8192 — the settled config, thinking off as on every sheet. The belief sensitivity measured for Gemma has not been measured for Qwen; Deepseek reasons and Qwen does not.</t>
+          <t>NEG_XAI, xai_sdk, max_tokens=8192, temperature 0, 0 empty. The first full run left 12,040 rows empty when the xAI credits ran out (ISSUES.md, 2026-07-29); the current shards have none. The *.STALE_pre20260729 roll-ups and *.jsonl.bak files beside them are that earlier run and are not the source. Not in Final_result.xlsx since 2026-10-05.</t>
         </is>
       </c>
     </row>
@@ -3671,17 +3718,17 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Qwen</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>14,138 rows — complete; belief caveat</t>
+          <t>14,138 rows — complete</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>NEG_Gemma, 14,138 rows, 0 empty. Together route with reasoning={"enabled": False}: thinking off, the same regime as Gemma's settled DeepInfra config on every other sheet (DeepInfra serves this checkpoint with thinking off), but not the same route. BELIEF IS SENSITIVE TO THAT SETTING: on 463 uids paired against an archived reasoning-on pilot, belief scored 0.6177 with reasoning on against 0.4903 off (McNemar p=1.2e-08). So Belief_EM 0.5007, and All_EM, which needs belief, describe Gemma at thinking off, not at its ceiling. Reported at the settled config by the user's decision on 2026-10-05 — ISSUES.md, "Gemma full run finished clean but belief is not usable as published".</t>
+          <t>NEG_Qwen, 14,138 rows, 0 empty. Together, reasoning={"enabled": False}, max_tokens=8192 — the settled config, thinking off as on every sheet. The belief sensitivity measured for Gemma has not been measured for Qwen; Deepseek reasons and Qwen does not.</t>
         </is>
       </c>
     </row>
@@ -3693,17 +3740,17 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Deepseek</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>14,138 rows — complete</t>
+          <t>14,138 rows — complete; belief caveat</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>NEG_Deepseek, 14,138 rows, 0 empty. DeepSeek API, max_tokens=8192, temperature 0. Reasoning is the model and has no knob.</t>
+          <t>NEG_Gemma, 14,138 rows, 0 empty. Together route with reasoning={"enabled": False}: thinking off, the same regime as Gemma's settled DeepInfra config on every other sheet (DeepInfra serves this checkpoint with thinking off), but not the same route. BELIEF IS SENSITIVE TO THAT SETTING: on 463 uids paired against an archived reasoning-on pilot, belief scored 0.6177 with reasoning on against 0.4903 off (McNemar p=1.2e-08). So Belief_EM 0.5007, and All_EM, which needs belief, describe Gemma at thinking off, not at its ceiling. Reported at the settled config by the user's decision on 2026-10-05 — ISSUES.md, "Gemma full run finished clean but belief is not usable as published".</t>
         </is>
       </c>
     </row>
@@ -3715,37 +3762,59 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Gemini-2.5-Flash · GPT-4o-mini</t>
+          <t>Deepseek</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>14,138 rows each — superseded</t>
+          <t>14,138 rows — complete</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>NEG_Gemini (gemini-2.5-flash, google-genai, thinking_budget=0) and NEG_GPT (gpt-4o-mini, max_tokens=8192), both 0 empty. Gemini's first run left 1,963 rows empty against the 10,000/day cap (ISSUES.md, 2026-07-29); the current shards have none. Both are superseded and kept as their own columns rather than filling the slots their replacements will hold.</t>
+          <t>NEG_Deepseek, 14,138 rows, 0 empty. DeepSeek API, max_tokens=8192, temperature 0. Reasoning is the model and has no knob.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
+          <t>NegotiationToM</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Gemini-2.5-Flash · GPT-4o-mini</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>14,138 rows each — superseded</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>NEG_Gemini (gemini-2.5-flash, google-genai, thinking_budget=0) and NEG_GPT (gpt-4o-mini, max_tokens=8192), both 0 empty. Gemini's first run left 1,963 rows empty against the 10,000/day cap (ISSUES.md, 2026-07-29); the current shards have none. Both are superseded and kept as their own columns rather than filling the slots their replacements will hold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
           <t>Awareness</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>every column</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>blank</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>No model has been scored yet; awareness_results.csv holds only the paper baselines.</t>
         </is>

--- a/Tempo_results.xlsx
+++ b/Tempo_results.xlsx
@@ -2940,12 +2940,12 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>gemini-3.5-flash-lite</t>
+          <t>gemini-3.5-flash-lite (OpenRouter, minimal)</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>gpt-5.6-luna</t>
+          <t>gpt-5.6-luna (effort=low)</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
@@ -2955,17 +2955,17 @@
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>Qwen/Qwen3.5-9B</t>
+          <t>Qwen/Qwen3.5-9B (reasoning off)</t>
         </is>
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>google/gemma-4-31B-it</t>
+          <t>google/gemma-4-31B-it (DeepInfra)</t>
         </is>
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-flash (prompt ceiling)</t>
         </is>
       </c>
     </row>
@@ -2975,6 +2975,21 @@
           <t>capability</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>0.6338</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.5268</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.6237</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9064</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9181</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2982,6 +2997,21 @@
           <t>mission_explicit</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>0.9928</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.9969</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9959</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2989,6 +3019,21 @@
           <t>mission_implicit</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>0.9226</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8418</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9428</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9933</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9428</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3003,12 +3048,22 @@
           <t>mission</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
+      <c r="B7" s="3" t="n">
+        <v>0.9577</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.9193</v>
+      </c>
       <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
+      <c r="E7" s="3" t="n">
+        <v>0.9693000000000001</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.9966</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0.9714</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3016,6 +3071,21 @@
           <t>emotion</t>
         </is>
       </c>
+      <c r="B8" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.93</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3023,6 +3093,21 @@
           <t>culture</t>
         </is>
       </c>
+      <c r="B9" t="n">
+        <v>0.9674</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9674</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9579</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9713000000000001</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.954</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3030,6 +3115,21 @@
           <t>perspective (2nd-order)</t>
         </is>
       </c>
+      <c r="B10" t="n">
+        <v>0.4941</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.6059</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1294</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8058999999999999</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3037,12 +3137,22 @@
           <t>Overall Score</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
+      <c r="B11" s="3" t="n">
+        <v>0.7936</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0.7909</v>
+      </c>
       <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
+      <c r="E11" s="3" t="n">
+        <v>0.6912</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0.7897</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0.9159</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3055,7 +3165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3067,7 +3177,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Tempo_results.xlsx — Every model that has appeared in an experiment. Rebuilt 2026-08-29 from the result files on disk; bbh refreshed 2026-09-07; NegotiationToM added 2026-10-05.</t>
+          <t>Tempo_results.xlsx — Every model that has appeared in an experiment. Rebuilt 2026-08-29 from the result files on disk; bbh refreshed 2026-09-07; NegotiationToM added 2026-10-05; Awareness added 2026-10-12.</t>
         </is>
       </c>
     </row>
@@ -3811,12 +3921,144 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>Transition_processes_benchmarks/Awareness_in_LLM/AWARE_*/results/&lt;task&gt;/&lt;slug&gt;.jsonl</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>No model has been scored yet; awareness_results.csv holds only the paper baselines.</t>
+          <t>Added 2026-10-12 from the first full run, recomputed from the per-task rows and checked equal to every AWARE_*/results/&lt;slug&gt;_awareness_overall.csv. Every column is the full 4,015 rows (3,975 after exact-duplicate dedup, 2,240 questions), 0 empty, one config per model, scorer aware_lenient_v4. Permuted tasks are permutation-averaged per question. mission = mean(explicit, implicit); perspective = the 170 second-order story rows; Overall Score = mean of capability, mission, emotion, perspective and culture. The run's record is Awareness_in_LLM/FULL_RUN_NOTES.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>mission_open-ended</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>blank — dropped by decision</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Its 60 rows are the only LLM-judged items; they were dropped on 2026-10-05, so this row stays blank for every model and mission is the two-term mean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Qwen — perspective 0</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>AWARE_Qwen, 170 of 170 second-order rows declined</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>A real refusal, kept as scored by the user's decision 2026-10-12. Every reply says the story gives no information about the character's thoughts; none gives an answer. Diagnosed on 10 items: it persists on another host, at temperature 0.7 and with reasoning on, and disappears with a larger Qwen3.5 or when the prompt states ToMi's rule that characters see what happens in their room (6/10 right). Without perspective Qwen's four-dimension mean is 0.864. FULL_RUN_NOTES.md §3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>perspective — what it measures</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>reasoning and refusals as much as theory of mind</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>Reasoning tokens per second-order item: Deepseek 1,465, OpenAI 179, Gemini/Gemma/Qwen 0. Gemma declined 124 of 170. Some second-order gold labels contradict their story; how many is unmeasured (FULL_RUN_NOTES.md §4–5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Gemini = gemini-3.5-flash-lite</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>4,015 rows — complete; resumed once</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>AWARE_Gemini_Flash3.5lite_OpenRouter, reasoning effort minimal, max_tokens=2048, seed 42. Job 9617441 stopped when the OpenRouter credit ran out (HTTP 402); resumed as 9645112 after a top-up, keeping its rows and retrying the 16 written empty. Parse-fail rate 0.8%, the highest of the five: half are refusals, half readable answers scorer v4 misses (FULL_RUN_NOTES.md §6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Deepseek</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>AWARE_Deepseek, model id deepseek-flash</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Called by its real id, deepseek-flash, which deepseek-reasoner (row 2, the slot's id on every sheet) now aliases (user's decision 2026-10-12). 'Think briefly' system message, max_tokens=8192, temperature 0, seed 42; reasoning is on and has no knob.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>scoring</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>aware_lenient_v4 — one known gap</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>39 of 20,075 rows are parse failures although an answer can be read; about 18 would turn correct, at most 1.2 points on a scored task. Not applied: these numbers are v4. A fix is a rescore from raw_response, never a rerun (FULL_RUN_NOTES.md §6).</t>
         </is>
       </c>
     </row>

--- a/Tempo_results.xlsx
+++ b/Tempo_results.xlsx
@@ -2703,7 +2703,7 @@
       </c>
       <c r="C2" s="11" t="inlineStr">
         <is>
-          <t>gpt-5.6-luna</t>
+          <t>gpt-5.6-luna (effort=low)</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
@@ -2744,7 +2744,9 @@
         </is>
       </c>
       <c r="B3" s="13" t="n"/>
-      <c r="C3" s="13" t="n"/>
+      <c r="C3" s="13" t="n">
+        <v>0.652</v>
+      </c>
       <c r="D3" s="13" t="n">
         <v>0.5393</v>
       </c>
@@ -2771,7 +2773,9 @@
         </is>
       </c>
       <c r="B4" s="13" t="n"/>
-      <c r="C4" s="13" t="n"/>
+      <c r="C4" s="13" t="n">
+        <v>0.6405</v>
+      </c>
       <c r="D4" s="13" t="n">
         <v>0.551</v>
       </c>
@@ -2798,7 +2802,9 @@
         </is>
       </c>
       <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
+      <c r="C5" s="13" t="n">
+        <v>0.5215</v>
+      </c>
       <c r="D5" s="13" t="n">
         <v>0.5382</v>
       </c>
@@ -2825,7 +2831,9 @@
         </is>
       </c>
       <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
+      <c r="C6" s="13" t="n">
+        <v>0.5012</v>
+      </c>
       <c r="D6" s="13" t="n">
         <v>0.5366</v>
       </c>
@@ -2852,7 +2860,9 @@
         </is>
       </c>
       <c r="B7" s="14" t="n"/>
-      <c r="C7" s="14" t="n"/>
+      <c r="C7" s="14" t="n">
+        <v>0.0765</v>
+      </c>
       <c r="D7" s="14" t="n">
         <v>0.0702</v>
       </c>
@@ -3165,7 +3175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3784,17 +3794,17 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Gemini · OpenAI</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>blank — the selected pair has not run</t>
+          <t>14,138 rows — complete</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>NEG_Gemini_Flash3.5lite_OpenRouter and NEG_GPT_5.6_Luna exist as runners (written 2026-09-11) and have been neither piloted nor run. The NEG_Gemini and NEG_GPT runs on disk are gemini-2.5-flash and gpt-4o-mini, both superseded; their numbers are in Tempo_results.xlsx only.</t>
+          <t>NEG_GPT_5.6_Luna, Quest job 9644711 (5 shards, 2026-10-12), merged 4,760 / 4,760 / 4,618, 0 empty, 0 parse fails, 0 truncated. reasoning_effort=low, max_completion_tokens=8192, seed 42 — negotiated identically on every shard; the settled config, as on every other sheet. Scores recomputed from the merged rows through the core's scorer and all_em, equal to gpt-5_6-luna_negotiation_overall.csv.</t>
         </is>
       </c>
     </row>
@@ -3806,17 +3816,17 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>XAI = grok-3-mini</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>14,138 rows — complete</t>
+          <t>blank — full run in progress</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>NEG_XAI, xai_sdk, max_tokens=8192, temperature 0, 0 empty. The first full run left 12,040 rows empty when the xAI credits ran out (ISSUES.md, 2026-07-29); the current shards have none. The *.STALE_pre20260729 roll-ups and *.jsonl.bak files beside them are that earlier run and are not the source. Not in Final_result.xlsx since 2026-10-05.</t>
+          <t>NEG_Gemini_Flash3.5lite_OpenRouter: pilot passed 2026-10-12 (1,416 rows, 0 empty, 0 truncated); the full run (Quest job 9682468) was submitted the same day. Blank until it finishes and is confirmed.</t>
         </is>
       </c>
     </row>
@@ -3828,7 +3838,7 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Qwen</t>
+          <t>XAI = grok-3-mini</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
@@ -3838,7 +3848,7 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>NEG_Qwen, 14,138 rows, 0 empty. Together, reasoning={"enabled": False}, max_tokens=8192 — the settled config, thinking off as on every sheet. The belief sensitivity measured for Gemma has not been measured for Qwen; Deepseek reasons and Qwen does not.</t>
+          <t>NEG_XAI, xai_sdk, max_tokens=8192, temperature 0, 0 empty. The first full run left 12,040 rows empty when the xAI credits ran out (ISSUES.md, 2026-07-29); the current shards have none. The *.STALE_pre20260729 roll-ups and *.jsonl.bak files beside them are that earlier run and are not the source. Not in Final_result.xlsx since 2026-10-05.</t>
         </is>
       </c>
     </row>
@@ -3850,17 +3860,17 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Qwen</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>14,138 rows — complete; belief caveat</t>
+          <t>14,138 rows — complete</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>NEG_Gemma, 14,138 rows, 0 empty. Together route with reasoning={"enabled": False}: thinking off, the same regime as Gemma's settled DeepInfra config on every other sheet (DeepInfra serves this checkpoint with thinking off), but not the same route. BELIEF IS SENSITIVE TO THAT SETTING: on 463 uids paired against an archived reasoning-on pilot, belief scored 0.6177 with reasoning on against 0.4903 off (McNemar p=1.2e-08). So Belief_EM 0.5007, and All_EM, which needs belief, describe Gemma at thinking off, not at its ceiling. Reported at the settled config by the user's decision on 2026-10-05 — ISSUES.md, "Gemma full run finished clean but belief is not usable as published".</t>
+          <t>NEG_Qwen, 14,138 rows, 0 empty. Together, reasoning={"enabled": False}, max_tokens=8192 — the settled config, thinking off as on every sheet. The belief sensitivity measured for Gemma has not been measured for Qwen; Deepseek reasons and Qwen does not.</t>
         </is>
       </c>
     </row>
@@ -3872,17 +3882,17 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Deepseek</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>14,138 rows — complete</t>
+          <t>14,138 rows — complete; belief caveat</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>NEG_Deepseek, 14,138 rows, 0 empty. DeepSeek API, max_tokens=8192, temperature 0. Reasoning is the model and has no knob.</t>
+          <t>NEG_Gemma, 14,138 rows, 0 empty. Together route with reasoning={"enabled": False}: thinking off, the same regime as Gemma's settled DeepInfra config on every other sheet (DeepInfra serves this checkpoint with thinking off), but not the same route. BELIEF IS SENSITIVE TO THAT SETTING: on 463 uids paired against an archived reasoning-on pilot, belief scored 0.6177 with reasoning on against 0.4903 off (McNemar p=1.2e-08). So Belief_EM 0.5007, and All_EM, which needs belief, describe Gemma at thinking off, not at its ceiling. Reported at the settled config by the user's decision on 2026-10-05 — ISSUES.md, "Gemma full run finished clean but belief is not usable as published".</t>
         </is>
       </c>
     </row>
@@ -3894,39 +3904,39 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Gemini-2.5-Flash · GPT-4o-mini</t>
+          <t>Deepseek</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>14,138 rows each — superseded</t>
+          <t>14,138 rows — complete</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>NEG_Gemini (gemini-2.5-flash, google-genai, thinking_budget=0) and NEG_GPT (gpt-4o-mini, max_tokens=8192), both 0 empty. Gemini's first run left 1,963 rows empty against the 10,000/day cap (ISSUES.md, 2026-07-29); the current shards have none. Both are superseded and kept as their own columns rather than filling the slots their replacements will hold.</t>
+          <t>NEG_Deepseek, 14,138 rows, 0 empty. DeepSeek API, max_tokens=8192, temperature 0. Reasoning is the model and has no knob.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>NegotiationToM</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>every column</t>
+          <t>Gemini-2.5-Flash · GPT-4o-mini</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Transition_processes_benchmarks/Awareness_in_LLM/AWARE_*/results/&lt;task&gt;/&lt;slug&gt;.jsonl</t>
+          <t>14,138 rows each — superseded</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Added 2026-10-12 from the first full run, recomputed from the per-task rows and checked equal to every AWARE_*/results/&lt;slug&gt;_awareness_overall.csv. Every column is the full 4,015 rows (3,975 after exact-duplicate dedup, 2,240 questions), 0 empty, one config per model, scorer aware_lenient_v4. Permuted tasks are permutation-averaged per question. mission = mean(explicit, implicit); perspective = the 170 second-order story rows; Overall Score = mean of capability, mission, emotion, perspective and culture. The run's record is Awareness_in_LLM/FULL_RUN_NOTES.md.</t>
+          <t>NEG_Gemini (gemini-2.5-flash, google-genai, thinking_budget=0) and NEG_GPT (gpt-4o-mini, max_tokens=8192), both 0 empty. Gemini's first run left 1,963 rows empty against the 10,000/day cap (ISSUES.md, 2026-07-29); the current shards have none. Both are superseded and kept as their own columns rather than filling the slots their replacements will hold.</t>
         </is>
       </c>
     </row>
@@ -3938,17 +3948,17 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>mission_open-ended</t>
+          <t>every column</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>blank — dropped by decision</t>
+          <t>Transition_processes_benchmarks/Awareness_in_LLM/AWARE_*/results/&lt;task&gt;/&lt;slug&gt;.jsonl</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Its 60 rows are the only LLM-judged items; they were dropped on 2026-10-05, so this row stays blank for every model and mission is the two-term mean.</t>
+          <t>Added 2026-10-12 from the first full run, recomputed from the per-task rows and checked equal to every AWARE_*/results/&lt;slug&gt;_awareness_overall.csv. Every column is the full 4,015 rows (3,975 after exact-duplicate dedup, 2,240 questions), 0 empty, one config per model, scorer aware_lenient_v4. Permuted tasks are permutation-averaged per question. mission = mean(explicit, implicit); perspective = the 170 second-order story rows; Overall Score = mean of capability, mission, emotion, perspective and culture. The run's record is Awareness_in_LLM/FULL_RUN_NOTES.md.</t>
         </is>
       </c>
     </row>
@@ -3960,17 +3970,17 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Qwen — perspective 0</t>
+          <t>mission_open-ended</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>AWARE_Qwen, 170 of 170 second-order rows declined</t>
+          <t>blank — dropped by decision</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>A real refusal, kept as scored by the user's decision 2026-10-12. Every reply says the story gives no information about the character's thoughts; none gives an answer. Diagnosed on 10 items: it persists on another host, at temperature 0.7 and with reasoning on, and disappears with a larger Qwen3.5 or when the prompt states ToMi's rule that characters see what happens in their room (6/10 right). Without perspective Qwen's four-dimension mean is 0.864. FULL_RUN_NOTES.md §3.</t>
+          <t>Its 60 rows are the only LLM-judged items; they were dropped on 2026-10-05, so this row stays blank for every model and mission is the two-term mean.</t>
         </is>
       </c>
     </row>
@@ -3982,17 +3992,17 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>perspective — what it measures</t>
+          <t>Qwen — perspective 0</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>reasoning and refusals as much as theory of mind</t>
+          <t>AWARE_Qwen, 170 of 170 second-order rows declined</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Reasoning tokens per second-order item: Deepseek 1,465, OpenAI 179, Gemini/Gemma/Qwen 0. Gemma declined 124 of 170. Some second-order gold labels contradict their story; how many is unmeasured (FULL_RUN_NOTES.md §4–5).</t>
+          <t>A real refusal, kept as scored by the user's decision 2026-10-12. Every reply says the story gives no information about the character's thoughts; none gives an answer. Diagnosed on 10 items: it persists on another host, at temperature 0.7 and with reasoning on, and disappears with a larger Qwen3.5 or when the prompt states ToMi's rule that characters see what happens in their room (6/10 right). Without perspective Qwen's four-dimension mean is 0.864. FULL_RUN_NOTES.md §3.</t>
         </is>
       </c>
     </row>
@@ -4004,17 +4014,17 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Gemini = gemini-3.5-flash-lite</t>
+          <t>perspective — what it measures</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>4,015 rows — complete; resumed once</t>
+          <t>reasoning and refusals as much as theory of mind</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>AWARE_Gemini_Flash3.5lite_OpenRouter, reasoning effort minimal, max_tokens=2048, seed 42. Job 9617441 stopped when the OpenRouter credit ran out (HTTP 402); resumed as 9645112 after a top-up, keeping its rows and retrying the 16 written empty. Parse-fail rate 0.8%, the highest of the five: half are refusals, half readable answers scorer v4 misses (FULL_RUN_NOTES.md §6).</t>
+          <t>Reasoning tokens per second-order item: Deepseek 1,465, OpenAI 179, Gemini/Gemma/Qwen 0. Gemma declined 124 of 170. Some second-order gold labels contradict their story; how many is unmeasured (FULL_RUN_NOTES.md §4–5).</t>
         </is>
       </c>
     </row>
@@ -4026,17 +4036,17 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Deepseek</t>
+          <t>Gemini = gemini-3.5-flash-lite</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>AWARE_Deepseek, model id deepseek-flash</t>
+          <t>4,015 rows — complete; resumed once</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Called by its real id, deepseek-flash, which deepseek-reasoner (row 2, the slot's id on every sheet) now aliases (user's decision 2026-10-12). 'Think briefly' system message, max_tokens=8192, temperature 0, seed 42; reasoning is on and has no knob.</t>
+          <t>AWARE_Gemini_Flash3.5lite_OpenRouter, reasoning effort minimal, max_tokens=2048, seed 42. Job 9617441 stopped when the OpenRouter credit ran out (HTTP 402); resumed as 9645112 after a top-up, keeping its rows and retrying the 16 written empty. Parse-fail rate 0.8%, the highest of the five: half are refusals, half readable answers scorer v4 misses (FULL_RUN_NOTES.md §6).</t>
         </is>
       </c>
     </row>
@@ -4048,15 +4058,37 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
+          <t>Deepseek</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>AWARE_Deepseek, model id deepseek-flash</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Called by its real id, deepseek-flash, which deepseek-reasoner (row 2, the slot's id on every sheet) now aliases (user's decision 2026-10-12). 'Think briefly' system message, max_tokens=8192, temperature 0, seed 42; reasoning is on and has no knob.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>aware_lenient_v4 — one known gap</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>39 of 20,075 rows are parse failures although an answer can be read; about 18 would turn correct, at most 1.2 points on a scored task. Not applied: these numbers are v4. A fix is a rescore from raw_response, never a rerun (FULL_RUN_NOTES.md §6).</t>
         </is>
